--- a/Outputs/Scenarios/PtX_demand_BE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BE_Electrification.xlsx
@@ -806,7 +806,7 @@
         <v>0.0001565817650843</v>
       </c>
       <c r="H10" t="n">
-        <v>0.003611508266197799</v>
+        <v>0.003611508266197801</v>
       </c>
       <c r="I10" t="n">
         <v>0.0100167268732999</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.009530239754080939</v>
+        <v>0.009530239754080938</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>

--- a/Outputs/Scenarios/PtX_demand_BE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BE_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001354470379864105</v>
       </c>
       <c r="K16" t="n">
-        <v>0.008624029714217206</v>
+        <v>0.009498761543690178</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001437338285702868</v>
+        <v>0.001872358979105462</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.005749353142811471</v>
+        <v>0.00748943591642185</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.008624029714217206</v>
+        <v>0.00748943591642185</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001085475088385503</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0120696742435677</v>
+        <v>0.01184949257896221</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0006570382993641298</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1167643914646922</v>
+        <v>0.1146343109372045</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>1.951562544001469e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001437338285702868</v>
+        <v>0.001872358979105462</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002005128495497259</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05065570830751732</v>
+        <v>0.05114738545340099</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.008442618051252888</v>
+        <v>0.0100819739469151</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.03377047220501155</v>
+        <v>0.04032789578766041</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.05065570830751732</v>
+        <v>0.04032789578766041</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001055330787103821</v>
       </c>
       <c r="K42" t="n">
-        <v>0.008442618051252888</v>
+        <v>0.0100819739469151</v>
       </c>
     </row>
     <row r="43">
